--- a/files_by_year/2024_randomsample.xlsx
+++ b/files_by_year/2024_randomsample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,96 +429,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Published Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Embargo Release</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>File Count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>File 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>File 2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>File 3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>File 4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>File 5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>File 6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>File 7</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>File 8</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>File 9</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>File 10</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>File 11</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>File 12</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>File 13</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -511,43 +532,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hh63sx250</t>
+          <t>3t945s235</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.18130/qm40-qd76</t>
+          <t>10.18130/jc9p-8606</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Allard_Tiara_STS Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Allard_Tiara_STS Research Paper.pdf</t>
+          <t>Zimnick_Kathryn_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Allard_Tiara_Sociotechnical Synthesis.pdf</t>
+          <t>Zimnick_Kathryn_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Allard_Tiara_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Zimnick_Kathryn_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Zimnick_Kathryn_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -556,50 +577,53 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xp68kh70r</t>
+          <t>0c483k875</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.18130/az0b-cg13</t>
+          <t>10.18130/y316-6e46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Al-Atrash_Muhammad_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>45606</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al-Atrash_Muhammad_STS Research Paper.pdf</t>
+          <t>DeCleene_Sophia_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Al-Atrash_Muhammad_Sociotechnical Synthesis.pdf</t>
+          <t>DeCleene_Sophia_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Al-Atrash_Muhammad_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>DeCleene_Sophia_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>DeCleene_Sophia_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -608,50 +632,51 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>b2773x229</t>
+          <t>cf95jc96r</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.18130/mepn-5m25</t>
+          <t>10.18130/n4s0-mm07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1_Skiles_John_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2_Skiles_John_2024_BS.pdf</t>
+          <t>Suwargo_Josiah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3_Skiles_John_2024_BS.pdf</t>
+          <t>Suwargo_Josiah_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4_Skiles_John_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Suwargo_Josiah_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Suwargo_Josiah_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -660,50 +685,51 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fj236364c</t>
+          <t>rb68xd42t</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.18130/ewn3-r641</t>
+          <t>10.18130/wym4-tc51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Schichtel_Connor_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Schichtel_Connor_STS Research Paper.pdf</t>
+          <t>Dulal_Krishna_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Schichtel_Connor_Sociotechnical Synthesis.pdf</t>
+          <t>Dulal_Krishna_STS Research.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schichtel_Connor_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Dulal_Krishna_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Dulal_Krishna_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -712,50 +738,51 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dn39x301t</t>
+          <t>ht24wk725</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.18130/k387-8s68</t>
+          <t>10.18130/68ct-cg76</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1_Choi_Daniel_2024_Research_Paper.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2_Choi_Daniel_2024_Prospectus.pdf</t>
+          <t>Cahill_Matthew_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3_Choi_Daniel_2024_Sociotechnical_Synthesis.pdf</t>
+          <t>Cahill_Matthew_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4_Choi_Daniel_2024_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Cahill_Matthew_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Cahill_Matthew_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -764,50 +791,51 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8623hz99b</t>
+          <t>hq37vp93p</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.18130/qckf-xa70</t>
+          <t>10.18130/gjkd-hj14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Marino_Collin_Executive_Summary.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Marino_Collin_Prospectus.pdf</t>
+          <t>Dhore_Aaryan_2024_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Marino_Collin_STS Research Paper.pdf</t>
+          <t>Dhore_Aaryan_2024_STS.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Marino_Collin_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Dhore_Aaryan_2024_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Dhore_Aaryan_2024_Technical.pdf</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -816,50 +844,51 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gt54kp39g</t>
+          <t>5q47rq12x</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.18130/1w6d-vd37</t>
+          <t>10.18130/d4ts-fe50</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Thielen_Jason_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thielen_Jason_STS_Research_Paper.pdf</t>
+          <t>Barnard-Davignon_Alexandria_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thielen_Jason_Sociotechnical_Synthesis.pdf</t>
+          <t>Barnard-Davignon_Alexandria_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Thielen_Jason_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Barnard-Davignon_Alexandria_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Barnard-Davignon_Alexandria_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -868,59 +897,54 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6q182m37k</t>
+          <t>2j62s641h</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.18130/c8n5-gw88</t>
+          <t>10.18130/yr6q-7331</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1_Eswarapragada_Karthik_2024_PortfolioCoverPage.pdf</t>
-        </is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2_Eswarapragada_Karthik_2024_Contents.pdf</t>
+          <t>Tierney_Evan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3_Eswarapragada_Karthik_2024_Preface.pdf</t>
+          <t>Tierney_Evan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4_Eswarapragada_Karthik_2024_Technical Report.pdf</t>
+          <t>Tierney_Evan_Sociotechnical Synthesis.pdf</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5_Eswarapragada_Karthik_2024_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6_Eswarapragada_Karthik_2024_Prospectus.pdf</t>
-        </is>
-      </c>
+          <t>Tierney_Evan_Technical Report.pdf</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -928,19 +952,20 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ff365675n</t>
+          <t>vq27zp879</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.18130/whtw-jc11</t>
+          <t>10.18130/0rv5-k430</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -948,30 +973,32 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hixson_Kaitlyn_Executive_Summary.pdf</t>
-        </is>
+      <c r="D10" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hixson_Kaitlyn_Prospectus.pdf</t>
+          <t>Cook_Christopher_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hixson_Kaitlyn_STS_Research_Paper.pdf</t>
+          <t>Cook_Christopher_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hixson_Kaitlyn_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Cook_Christopher_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Cook_Christopher_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -980,50 +1007,51 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>b2773x08g</t>
+          <t>g445cf72p</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.18130/zkgt-3w05</t>
+          <t>10.18130/c07s-2865</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1_Huang_Isabella_2024_BS.pdf</t>
-        </is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2_Huang_Isabella_2024_BS.pdf</t>
+          <t>Burroughs_Garrett_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3_Huang_Isabella_2024_BS.pdf</t>
+          <t>Burroughs_Garrett_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4_Huang_Isabella_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Burroughs_Garrett_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Burroughs_Garrett_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1032,50 +1060,51 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>df65v9101</t>
+          <t>pc289k70h</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.18130/b5pj-9y11</t>
+          <t>10.18130/b31d-k308</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Marasini_Rajan_Research_Paper.pdf</t>
-        </is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marasini_Rajan_STS_Prospectus.pdf</t>
+          <t>1_Petty_Lauren_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Marasini_Rajan_Sociotechnical_Synthesis.pdf</t>
+          <t>2_Petty_Lauren_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Marasini_Rajan_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>3_Petty_Lauren_Technical Report.pdf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4_Petty_Lauren_STS Research Paper.pdf</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1084,50 +1113,51 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6108vc416</t>
+          <t>mp48sf11p</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.18130/f9px-xv53</t>
+          <t>10.18130/1qgn-h079</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1_Wang_Leo_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2_Wang_Leo_2024_BS.pdf</t>
+          <t>Razavi_Nima_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3_Wang_Leo_2024_BS.pdf</t>
+          <t>Razavi_Nima_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4_Wang_Leo_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Razavi_Nima_STS_Technical_Report.pdf</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Razavi_Nima_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1136,50 +1166,51 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nc580p137</t>
+          <t>70795897t</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.18130/sw3r-yw38</t>
+          <t>10.18130/kzgw-c553</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Portuese_Spencer_2024_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Portuese_Spencer_2024_STS Research Paper.pdf</t>
+          <t>Merida_Santiago_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Portuese_Spencer_Sociotechnical Synthesis.pdf</t>
+          <t>Merida_Santiago_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Portuese_Spencer_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Merida_Santiago_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Merida_Santiago_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1188,19 +1219,20 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2v23vv881</t>
+          <t>dj52w6001</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.18130/w4k9-7k03</t>
+          <t>10.18130/f5x8-1j24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1208,30 +1240,30 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Goundry_Katherine_Prospectus.pdf</t>
-        </is>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goundry_Katherine_STS Research Paper.pdf</t>
+          <t>Leshok_Isaac_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goundry_Katherine_Sociotechnical Synthesis.pdf</t>
+          <t>Leshok_Isaac_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Goundry_Katherine_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Leshok_Isaac_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Leshok_Isaac_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1240,52 +1272,49 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>h702q779h</t>
+          <t>vd66w1391</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.18130/vc6t-st80</t>
+          <t>10.18130/r9m6-br30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1_Talton_Nicholas_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2_Talton_Nicholas_2024_BS.pdf</t>
+          <t>Bacica_Ethan_ExecutiveSummary.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3_Talton_Nicholas_2024_BS.pdf</t>
+          <t>Bacica_Ethan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4_Talton_Nicholas_2024_BS.pdf</t>
+          <t>Bacica_Ethan_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5_Talton_Nicholas_2024_BS.pdf</t>
+          <t>Bacica_Ethan_TechnicalReport.pdf</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1296,50 +1325,53 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jq085m451</t>
+          <t>m900nv825</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.18130/46e3-2x05</t>
+          <t>10.18130/pbw5-7h11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-05-14</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Hildebrand_Chase_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>45598</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hildebrand_Chase_STS Research Paper.pdf</t>
+          <t>Brett_Karin_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hildebrand_Chase_Sociotechnical Synthesis.pdf</t>
+          <t>Brett_Karin_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Hildebrand_Chase_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>Brett_Karin_Sociotechnical Thesis.pdf</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Brett_Karin_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1348,19 +1380,20 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ks65hd490</t>
+          <t>5t34sk90b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.18130/dcx2-xv83</t>
+          <t>10.18130/z8zp-tk62</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1368,30 +1401,30 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Vitchutripop_Teeratham_Prospectus.pdf</t>
-        </is>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitchutripop_Teeratham_STS Research Paper.pdf</t>
+          <t>Samuel_Matthew_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Vitchutripop_Teeratham_Sociotechnical Synthesis.pdf</t>
+          <t>Samuel_Matthew_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Vitchutripop_Teeratham_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Samuel_Matthew_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Samuel_Matthew_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1400,50 +1433,53 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>v118rg366</t>
+          <t>bk128c29h</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.18130/krtc-n328</t>
+          <t>10.18130/py5s-h292</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Desman_Braden_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>45787</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Desman_Braden_STS Research Paper.pdf</t>
+          <t>Gavin_Estrella_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Desman_Braden_Sociotechnical_Synthesis.pdf</t>
+          <t>Gavin_Estrella_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Desman_Braden_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Gavin_Estrella_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Gavin_Estrella_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1452,19 +1488,20 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wm117q37k</t>
+          <t>tb09j724j</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.18130/rt6t-xx96</t>
+          <t>10.18130/btvm-6p85</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1472,30 +1509,30 @@
           <t>2024-05-10</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Gundamraj_Rahul_Prospectus.pdf</t>
-        </is>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gundamraj_Rahul_STS Research Paper.pdf</t>
+          <t>1_Buckner_Ethan_2024_BS.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gundamraj_Rahul_Sociotechnical Synthesis.pdf</t>
+          <t>2_Buckner_Ethan_2024_BS.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Gundamraj_Rahul_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>3_Buckner_Ethan_2024_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4_Buckner_Ethan_2024_BS.pdf</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1504,50 +1541,53 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qf85nc672</t>
+          <t>ff365672t</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.18130/zm0m-mg51</t>
+          <t>10.18130/zd32-jz07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Zappia_Peter_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>45604</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zappia_Peter_STS Research Paper.pdf</t>
+          <t>Domer_Thomas_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Zappia_Peter_Sociotechnical Synthesis.pdf</t>
+          <t>Domer_Thomas_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Zappia_Peter_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Domer_Thomas_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Domer_Thomas_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1556,50 +1596,51 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qr46r2141</t>
+          <t>z890rv771</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.18130/4ver-wc85</t>
+          <t>10.18130/465r-m490</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Tuohy_Owen_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tuohy_Owen_STS_Research_Paper.pdf</t>
+          <t>Ahn_Samuel_Executive_Summary.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tuohy_Owen_Sociotechnical_Synthesis.pdf</t>
+          <t>Ahn_Samuel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tuohy_Owen_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Ahn_Samuel_STS_Research_Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Ahn_Samuel_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1608,50 +1649,53 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ff365676x</t>
+          <t>p5547s797</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.18130/f2zv-hm28</t>
+          <t>10.18130/e907-9t78</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Huang_Ningxi_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>45785</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Huang_Ningxi_STS_Research_Paper.pdf</t>
+          <t>Lin_David_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Huang_Ningxi_Sociotechnical_Synthesis.pdf</t>
+          <t>Lin_David_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Huang_Ningxi_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Lin_David_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Lin_David_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1660,50 +1704,51 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cc08hh19n</t>
+          <t>ht24wk814</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.18130/7w2f-7q65</t>
+          <t>10.18130/tvy9-k628</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-04-30</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Dhanasekar_Sadhika_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dhanasekar_Sadhika_STS Research Paper.pdf</t>
+          <t>STS Paper</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dhanasekar_Sadhika_Sociotechnical Synthesis.pdf</t>
+          <t>Sociotechnical Synthesis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Dhanasekar_Sadhika_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Technical Report</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Thesis Prospectus</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1712,50 +1757,51 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>js956h11d</t>
+          <t>3f462688z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.18130/19nc-fb84</t>
+          <t>10.18130/0zpe-xf93</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Borland_Katie_Executive Summary.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Borland_Katie_Prospectus.pdf</t>
+          <t>Barker_Dayton_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Borland_Katie_STS Research Paper.pdf</t>
+          <t>Barker_Dayton_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Borland_Katie_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Barker_Dayton_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Barker_Dayton_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1764,50 +1810,51 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vm40xt02p</t>
+          <t>sj139334d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.18130/xwfn-0r14</t>
+          <t>10.18130/dqz4-3v31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Li_Jet_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Li_Jet_STS Research Paper.pdf</t>
+          <t>Witter_Gabriel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Li_Jet_Sociotechnical Synthesis.pdf</t>
+          <t>Witter_Gabriel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Li_Jet_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Witter_Gabriel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Witter_Gabriel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1816,50 +1863,51 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f7623d96n</t>
+          <t>02870x47d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.18130/1wej-de30</t>
+          <t>10.18130/8fnd-ap12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1_Teller_Nick_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2_Teller_Nick_2024_BS.pdf</t>
+          <t>Miskinyar_Duraan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3_Teller_Nick_2024_BS.pdf</t>
+          <t>Miskinyar_Duraan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4_Teller_Nick_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Miskinyar_Duraan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Miskinyar_Duraan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1868,50 +1916,51 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9w032441x</t>
+          <t>4q77fs72h</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.18130/nnqd-by67</t>
+          <t>10.18130/yyzc-9z63</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Brown_Jessica_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brown_Jessica_STS Research Paper.pdf</t>
+          <t>Crawford_Leon_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Brown_Jessica_Synthesis.pdf</t>
+          <t>Crawford_Leon_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brown_Jessica_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Crawford_Leon_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Crawford_Leon_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1920,50 +1969,51 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2801ph64v</t>
+          <t>k0698878c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.18130/cvg2-gt65</t>
+          <t>10.18130/qna2-tf55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Carroll_Justin_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carroll_Justin_STS Research Paper.pdf</t>
+          <t>Branch_Stephen_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carroll_Justin_Sociotechnical Synthesis.pdf</t>
+          <t>Branch_Stephen_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Carroll_Justin_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Branch_Stephen_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Branch_Stephen_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1972,50 +2022,51 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mp48sf11p</t>
+          <t>6108vc37m</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.18130/1qgn-h079</t>
+          <t>10.18130/zn5k-2n44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Razavi_Nima_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Razavi_Nima_STS_Research_Paper.pdf</t>
+          <t>Lyall_Olivia_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Razavi_Nima_STS_Technical_Report.pdf</t>
+          <t>Lyall_Olivia_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Razavi_Nima_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Lyall_Olivia_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Lyall_Olivia_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2024,50 +2075,53 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>k0698879n</t>
+          <t>5425kc05x</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.18130/fypp-8y03</t>
+          <t>10.18130/4ere-qv04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Kim_Jonah_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kim_Jonah_STS Research Paper.pdf</t>
+          <t>Halliwill_Jack_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kim_Jonah_Sociotechnical Synthesis.pdf</t>
+          <t>Halliwill_Jack_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kim_Jonah_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Halliwill_Jack_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Halliwill_Jack_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2076,50 +2130,51 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4t64gp62h</t>
+          <t>xs55md476</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.18130/7jzp-r860</t>
+          <t>10.18130/z0c5-nt65</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Bigler-Wang_Benny_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bigler-Wang_Benny_STS Research Paper.pdf</t>
+          <t>Kumar_Aditya_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bigler-Wang_Benny_Sociotechnical Synthesis.pdf</t>
+          <t>Kumar_Aditya_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bigler-Wang_Benny_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Kumar_Aditya_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Kumar_Aditya_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2128,50 +2183,51 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>x059c859x</t>
+          <t>sn00b029s</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.18130/wavc-2h36</t>
+          <t>10.18130/55vc-8j88</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Hernandez_Spencer_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hernandez_Spencer_STS Research Paper.pdf</t>
+          <t>Wilson_Connor_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hernandez_Spencer_Sociotechnical Synthesis.pdf</t>
+          <t>Wilson_Connor_Sociotechnical Synthesis.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Hernandez_Spencer_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Wilson_Connor_Technical Report.pdf</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Wilson_Connor_Thesis Prospectus.pdf</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2180,19 +2236,20 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4x51hk339</t>
+          <t>kp78gh921</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.18130/hpa5-5j67</t>
+          <t>10.18130/ta0e-7z48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2200,30 +2257,30 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Price_Alex_Prospectus.pdf</t>
-        </is>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Price_Alex_STS Research Paper.pdf</t>
+          <t>Bristow_Decker_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Price_Alex_Sociotechnical Synthesis.pdf</t>
+          <t>Bristow_Decker_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Price_Alex_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Bristow_Decker_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Bristow_Decker_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2232,50 +2289,51 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3t945s392</t>
+          <t>vq27zp89v</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.18130/pxje-4744</t>
+          <t>10.18130/x2c0-q907</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Conway_Jared_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Conway_Jared_STS Research Paper.pdf</t>
+          <t>Bales_Jake_Prospectus</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Conway_Jared_Sociotechnical Synthesis.pdf</t>
+          <t>Bales_Jake_STS Research Paper</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Conway_Jared_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Bales_Jake_Sociotechnical Synthesis</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Bales_Jake_Technical Report</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2284,50 +2342,51 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gh93h0861</t>
+          <t>3f4626829</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10.18130/21bf-ey23</t>
+          <t>10.18130/bhhw-fc02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Workman_Anna_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Workman_Anna_STS Research Paper.pdf</t>
+          <t>Malanga_Luke_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Workman_Anna_Sociotechnical Synthesis.pdf</t>
+          <t>Malanga_Luke_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Workman_Anna_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Malanga_Luke_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Malanga_Luke_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2336,50 +2395,53 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>9c67wp14m</t>
+          <t>st74cs01n</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.18130/r6g6-1706</t>
+          <t>10.18130/pdrc-0d85</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>1_Dollahite_Rebecca_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2_Dollahite_Rebecca_2024_BS.pdf</t>
+          <t>Burre_Sidhardh_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3_Dollahite_Rebecca_2024_BS.pdf</t>
+          <t>Burre_Sidhardh_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4_Dollahite_Rebecca_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Burre_Sidhardh_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Burre_Sidhardh_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2388,50 +2450,53 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8623j009j</t>
+          <t>hh63sx250</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.18130/7fxv-9175</t>
+          <t>10.18130/qm40-qd76</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Ko_Aaron_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ko_Aaron_STS Research Paper.pdf</t>
+          <t>Allard_Tiara_STS Prospectus.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ko_Aaron_Sociotechnical Synthesis.pdf</t>
+          <t>Allard_Tiara_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Ko_Aaron_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Allard_Tiara_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Allard_Tiara_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2440,19 +2505,20 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>z316q304f</t>
+          <t>h415pc077</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.18130/jq50-1q91</t>
+          <t>10.18130/p297-kp81</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2460,30 +2526,32 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Kent_Claire_Executive Summary.pdf</t>
-        </is>
+      <c r="D39" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kent_Claire_Prospectus.pdf</t>
+          <t>Lothrop_Connor_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Kent_Claire_STS Research Paper.pdf</t>
+          <t>Lothrop_Connor_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kent_Claire_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Lothrop_Connor_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Lothrop_Connor_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2492,50 +2560,53 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>9p290b961</t>
+          <t>3484zj28k</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.18130/v1f2-zm20</t>
+          <t>10.18130/dpk1-fb44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Madhav_Amish_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Madhav_Amish_STS Research Paper.pdf</t>
+          <t>Li_Eric_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Madhav_Amish_Sociotechnical Synthesis.pdf</t>
+          <t>Li_Eric_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Madhav_Amish_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Li_Eric_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Li_Eric_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2544,50 +2615,51 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4t64gp54t</t>
+          <t>zp38wf084</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.18130/yhzf-er31</t>
+          <t>10.18130/qbky-hk44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>4_Johnson_Alexander_Technical Report.pdf</t>
-        </is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Johnson_Alexander_Prospectus.pdf</t>
+          <t>Klem_Stephen_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Johnson_Alexander_STS Research Paper.pdf</t>
+          <t>Klem_Stephen_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Johnson_Alexander_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Klem_Stephen_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Klem_Stephen_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2596,50 +2668,51 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9s1617704</t>
+          <t>wd375x60w</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.18130/c2kv-ee56</t>
+          <t>10.18130/1zqv-qz30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Khosbayar_Joe_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Khosbayar_Joe_STS_Research_Paper.pdf</t>
+          <t>Mendoza_Jassiel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Khosbayar_Joe_Sociotechnical_Synthesis.pdf</t>
+          <t>Mendoza_Jassiel_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Khosbayar_Joe_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Mendoza_Jassiel_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Mendoza_Jassiel_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2648,50 +2721,53 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2r36v0001</t>
+          <t>h128ng070</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.18130/ckm2-ty35</t>
+          <t>10.18130/fwm0-gk44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Patel_Isha_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>45601</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Patel_Isha_STSResearchPaper.pdf</t>
+          <t>Beall_Charles_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Patel_Isha_Sociotechnical_Synthesis.pdf</t>
+          <t>Beall_Charles_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Patel_Isha_TechnicalResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Beall_Charles_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Beall_Charles_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2700,19 +2776,20 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="n">
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gb19f7252</t>
+          <t>gf06g408n</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.18130/d458-ve33</t>
+          <t>10.18130/78zr-d317</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2720,30 +2797,30 @@
           <t>2024-05-08</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Vu_Tho_Prospectus.pdf</t>
-        </is>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vu_Tho_STS Research Paper.pdf</t>
+          <t>Dirting_Adam_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Vu_Tho_Sociotechnical Synthesis.pdf</t>
+          <t>Dirting_Adam_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Vu_Tho_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Dirting_Adam_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Dirting_Adam_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2752,50 +2829,51 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sj139334d</t>
+          <t>c247dt440</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.18130/dqz4-3v31</t>
+          <t>10.18130/mycb-w706</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Witter_Gabriel_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Witter_Gabriel_STS Research Paper.pdf</t>
+          <t>Luu_Olivia_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Witter_Gabriel_Sociotechnical Synthesis.pdf</t>
+          <t>Luu_Olivia_Sociotechnical Research Paper.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Witter_Gabriel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Luu_Olivia_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Luu_Olivia_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2804,50 +2882,53 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>w9505202v</t>
+          <t>vd66w1412</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10.18130/4x49-g508</t>
+          <t>10.18130/eqjv-y179</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Yao_Emily_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>45600</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Yao_Emily_STS Research Paper.pdf</t>
+          <t>Robins_River_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yao_Emily_Sociotechnical Thesis.pdf</t>
+          <t>Robins_River_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Yao_Emily_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Robins_River_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Robins_River_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2856,50 +2937,53 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>st74cs01n</t>
+          <t>nv935458t</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.18130/pdrc-0d85</t>
+          <t>10.18130/be23-1214</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Burre_Sidhardh_Executive Summary.pdf</t>
-        </is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>45703</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burre_Sidhardh_Prospectus.pdf</t>
+          <t>Rasmussen_Tyler_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Burre_Sidhardh_STS Research Paper.pdf</t>
+          <t>Rasmussen_Tyler_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Burre_Sidhardh_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Rasmussen_Tyler_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Rasmussen_Tyler_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2908,50 +2992,51 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="n">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>xd07gv32k</t>
+          <t>2r36tz96g</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.18130/8va5-ts20</t>
+          <t>10.18130/bvr3-r609</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Bae_David_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bae_David_Research Paper.pdf</t>
+          <t>Steere_Ethan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bae_David_Sociotechnical Synthesis.pdf</t>
+          <t>Steere_Ethan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bae_David_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Steere_Ethan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Steere_Ethan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2960,50 +3045,51 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>q237ht515</t>
+          <t>1r66j2315</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10.18130/g2rp-5611</t>
+          <t>10.18130/46j5-qj48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Swart_Audrey_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Swart_Audrey_STS_Research_Paper.pdf</t>
+          <t>Blackman_Cole_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Swart_Audrey_Sociotechnical_Synthesis.pdf</t>
+          <t>Blackman_Cole_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Swart_Audrey_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Blackman_Cole_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Blackman_Cole_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3012,19 +3098,20 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="n">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2v23vv82c</t>
+          <t>0z708x955</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10.18130/x36e-7h73</t>
+          <t>10.18130/35vb-7t19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3032,30 +3119,32 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Lu_Gabriel_Prospectus.pdf</t>
-        </is>
+      <c r="D50" s="2" t="n">
+        <v>45786</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lu_Gabriel_STS Research Paper.pdf</t>
+          <t>Powell_Isabella_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lu_Gabriel_Sociotechnical Synthesis.pdf</t>
+          <t>Powell_Isabella_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lu_Gabriel_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Powell_Isabella_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Powell_Isabella_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3064,19 +3153,20 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nc580p19w</t>
+          <t>zk51vj240</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10.18130/j7tq-8773</t>
+          <t>10.18130/wf08-9358</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3084,30 +3174,30 @@
           <t>2024-05-08</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Jiang_Peter_Prospectus.pdf</t>
-        </is>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Jiang_Peter_STS Research Paper.pdf</t>
+          <t>Yu_Joshua_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Jiang_Peter_Sociotechnical Synthesis.pdf</t>
+          <t>Yu_Joshua_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Jiang_Peter_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Yu_Joshua_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Yu_Joshua_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3116,50 +3206,51 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>bv73c1786</t>
+          <t>7p88cj029</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10.18130/mx7h-vs85</t>
+          <t>10.18130/p3tp-2734</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Daigneau_Troy_Executive Summary.pdf</t>
-        </is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Daigneau_Troy_Prospectus.pdf</t>
+          <t>Capstone_Lawrence_Gabriel_2024_BS.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Daigneau_Troy_STS Research Paper.pdf</t>
+          <t>Prospectus_LawrenceGabriel2024.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Daigneau_Troy_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Synthesis_LawrenceGabriel2024.pdf</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Thesis_LawrenceGabriel2024.pdf</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3168,50 +3259,51 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3484zj22x</t>
+          <t>9w032441x</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10.18130/qh3a-s922</t>
+          <t>10.18130/nnqd-by67</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Freeman_Ahava_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Freeman_Ahava_STS Research Paper.pdf</t>
+          <t>Brown_Jessica_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Freeman_Ahava_Sociotechnical Synthesis.pdf</t>
+          <t>Brown_Jessica_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Freeman_Ahava_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Brown_Jessica_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Brown_Jessica_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3220,50 +3312,51 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>n870zs13k</t>
+          <t>j96022066</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10.18130/cp72-3z29</t>
+          <t>10.18130/ar0z-s258</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1_Holloman_Bella_2024_BS.pdf</t>
-        </is>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2_Holloman_Bella_2024_BS.pdf</t>
+          <t>Urbanowski_Kamil_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3_Holloman_Bella_2024_BS.pdf</t>
+          <t>Urbanowski_Kamil_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4_Holloman_Bella_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Urbanowski_Kamil_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Urbanowski_Kamil_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3272,50 +3365,53 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0c483k875</t>
+          <t>rj4305894</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10.18130/y316-6e46</t>
+          <t>10.18130/t8cf-bd46</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>DeCleene_Sophia_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>DeCleene_Sophia_STS Research Paper.pdf</t>
+          <t>Wigode_Evan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DeCleene_Sophia_Sociotechnical Synthesis.pdf</t>
+          <t>Wigode_Evan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>DeCleene_Sophia_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Wigode_Evan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Wigode_Evan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3324,50 +3420,51 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2j62s648f</t>
+          <t>3t945s392</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.18130/2qhz-3542</t>
+          <t>10.18130/pxje-4744</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Tremblay_Beatrice_Prospectus.pdf</t>
-        </is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tremblay_Beatrice_STS Research Paper.pdf</t>
+          <t>Conway_Jared_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tremblay_Beatrice_Sociotechnical Synthesis.pdf</t>
+          <t>Conway_Jared_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tremblay_Beatrice_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Conway_Jared_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Conway_Jared_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3376,50 +3473,51 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>m900nv88t</t>
+          <t>x633f234j</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10.18130/hfgw-0c05</t>
+          <t>10.18130/6rd9-yc07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Mirza_Rafid_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mirza_Rafid_STS Research Paper.pdf</t>
+          <t>Patton_Nathan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mirza_Rafid_Sociotechnical Synthesis.pdf</t>
+          <t>Patton_Nathan_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Mirza_Rafid_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Patton_Nathan_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Patton_Nathan_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3428,50 +3526,53 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="n">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>r494vm56d</t>
+          <t>9z903140v</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10.18130/yahj-4j87</t>
+          <t>10.18130/2dbc-gh43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Choubah_Sacha_Prospectus.pdf</t>
-        </is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Choubah_Sacha_STS Research Paper.pdf</t>
+          <t>Harvey_Ian_Executive Summary.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Choubah_Sacha_Sociotechnical Synthesis.pdf</t>
+          <t>Harvey_Ian_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Choubah_Sacha_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Harvey_Ian_STS Research Paper.pdf</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Harvey_Ian_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3480,19 +3581,20 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
         <v>2024</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sf268644d</t>
+          <t>ht24wk73f</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10.18130/bdrn-3155</t>
+          <t>10.18130/1xbv-8660</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3500,30 +3602,30 @@
           <t>2024-05-09</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Qamar_Sunya_Prospectus.pdf</t>
-        </is>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Qamar_Sunya_STS Research Paper.pdf</t>
+          <t>Hawkins_Alex_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Qamar_Sunya_Sociotechnical Synthesis.pdf</t>
+          <t>Hawkins_Alex_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Qamar_Sunya_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Hawkins_Alex_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Hawkins_Alex_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3532,631 +3634,8 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>q524jq16t</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>10.18130/x0wv-aa09</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Browder_Charlotte_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Browder_Charlotte_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Browder_Charlotte_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Browder_Charlotte_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>sb3979577</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>10.18130/384f-gw18</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Loayza_Angie_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Loayza_Angie_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Loayza_Angie_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Loayza_Angie_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1831cm32x</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>10.18130/bxd2-m913</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Page_Hayden_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Page_Hayden_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Page_Hayden_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Page_Hayden_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>8p58pf479</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>10.18130/tmad-2n13</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Megerssa_Janco_2024_Executive_Summary.pdf</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Megerssa_Janco_2024_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Megerssa_Janco_2024_STS_Research_Paper.pdf</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Megerssa_Janco_2024_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>p8418p75c</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>10.18130/p9m2-5538</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Cook_Thomas_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Cook_Thomas_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Cook_Thomas_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Cook_Thomas_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2v23vv87r</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>10.18130/zpqt-me97</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Marinaro_Christian_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Marinaro_Christian_STS_Research_Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Marinaro_Christian_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Verma_Marinaro_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>h128ng06q</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>10.18130/tqcr-1m33</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Moskowitz_Aydan_ExecutiveSummary.pdf</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Moskowitz_Aydan_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Moskowitz_Aydan_STSResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Moskowitz_Aydan_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>s7526d80h</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>10.18130/xt6v-f328</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2024-05-07</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Orellana_Ronald_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Orellana_Ronald_STS_Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Orellana_Ronald_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Orellana_Ronald_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>8623hz97s</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>10.18130/st68-8z81</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Tam_Keith_2024_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tam_Keith_2024_STSResearchPaper.pdf</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Tam_Keith_2024_SociotechnicalSynthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Tam_Keith_2024_TechnicalReport.pdf</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2801ph67p</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>10.18130/njbp-ef03</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1_Ackley_Michael_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2_Ackley_Michael_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>3_Ackley_Michael_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>4_Ackley_Michael_2024_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>4t64gp66m</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>10.18130/vsyk-5006</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Brightwell_Marc_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Brightwell_Marc_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Brightwell_Marc_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Brightwell_Marc_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>d504rm75w</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>10.18130/dr7m-md64</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2024-05-10</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Kuzjak_Matthew_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Kuzjak_Matthew_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Kuzjak_Matthew_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kuzjak_Matthew_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="n">
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
         <v>2024</v>
       </c>
     </row>
